--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_tn_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_tn_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>21-04-2021 08:30</t>
+          <t>2021-04-21 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -725,7 +725,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>21-04-2021 08:30</t>
+          <t>2021-04-21 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>19-05-2021 08:30</t>
+          <t>2021-05-19 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="inlineStr"/>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9652,7 +9652,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9745,7 +9745,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="inlineStr"/>
@@ -10117,7 +10117,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="inlineStr"/>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="inlineStr"/>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -10489,7 +10489,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -10675,7 +10675,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -10861,7 +10861,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="inlineStr"/>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -11233,7 +11233,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="inlineStr"/>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="inlineStr"/>
@@ -11419,7 +11419,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="inlineStr"/>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="inlineStr"/>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="inlineStr"/>
@@ -12442,7 +12442,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="inlineStr"/>
@@ -12535,7 +12535,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12628,7 +12628,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>21-04-2021 08:30</t>
+          <t>2021-04-21 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
@@ -12913,7 +12913,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -13006,7 +13006,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="inlineStr"/>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="inlineStr"/>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="inlineStr"/>
@@ -13285,7 +13285,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="inlineStr"/>
@@ -13477,7 +13477,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="inlineStr"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="inlineStr"/>
@@ -13663,7 +13663,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="inlineStr"/>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="inlineStr"/>
@@ -13849,7 +13849,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="inlineStr"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>25-08-2021 08:30</t>
+          <t>2021-08-25 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14607,7 +14607,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>27-09-2021 08:30</t>
+          <t>2021-09-27 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -14987,7 +14987,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="inlineStr"/>
@@ -15181,7 +15181,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr"/>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr"/>
@@ -15367,7 +15367,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -15460,7 +15460,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr"/>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -15739,7 +15739,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="inlineStr"/>
@@ -15832,7 +15832,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="inlineStr"/>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16024,7 +16024,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="inlineStr"/>
@@ -16216,7 +16216,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="inlineStr"/>
@@ -16309,7 +16309,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="inlineStr"/>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -16703,7 +16703,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -17083,7 +17083,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17273,7 +17273,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17368,7 +17368,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="n">
@@ -17463,7 +17463,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="n">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="n">
@@ -17653,7 +17653,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -17748,7 +17748,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="inlineStr"/>
@@ -17936,7 +17936,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18037,7 +18037,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18233,7 +18233,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18328,7 +18328,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18423,7 +18423,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="n">
@@ -18518,7 +18518,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="n">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -18708,7 +18708,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="n">
@@ -18803,7 +18803,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="n">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="n">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="n">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="n">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="n">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="n">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="n">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="n">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="n">
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="n">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="n">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="n">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="n">
@@ -20323,7 +20323,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="n">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="n">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="n">
@@ -20608,7 +20608,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="n">
@@ -20703,7 +20703,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="n">
@@ -20798,7 +20798,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="n">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="n">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="n">
@@ -21083,7 +21083,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="n">
@@ -21178,7 +21178,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="n">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="n">
@@ -21368,7 +21368,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="n">
@@ -21463,7 +21463,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="n">
@@ -21558,7 +21558,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="n">
@@ -21653,7 +21653,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="n">
@@ -21748,7 +21748,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="n">
@@ -21843,7 +21843,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="n">
@@ -21938,7 +21938,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="n">
@@ -22033,7 +22033,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="n">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="n">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="n">
@@ -22318,7 +22318,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="n">
@@ -22413,7 +22413,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="n">
@@ -22508,7 +22508,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="n">
@@ -22603,7 +22603,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="n">
@@ -22698,7 +22698,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="inlineStr"/>
@@ -22791,7 +22791,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr"/>
@@ -22884,7 +22884,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -22977,7 +22977,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr"/>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -23163,7 +23163,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="inlineStr"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="inlineStr"/>
@@ -23349,7 +23349,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="inlineStr"/>
@@ -23442,7 +23442,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="inlineStr"/>
@@ -23535,7 +23535,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="inlineStr"/>
@@ -23628,7 +23628,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="inlineStr"/>
@@ -23721,7 +23721,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="inlineStr"/>
@@ -23814,7 +23814,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="inlineStr"/>
@@ -23907,7 +23907,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="inlineStr"/>
@@ -24000,7 +24000,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>30-03-2021 08:30</t>
+          <t>2021-03-30 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="inlineStr"/>
@@ -24093,7 +24093,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="inlineStr"/>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="inlineStr"/>
@@ -24279,7 +24279,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="inlineStr"/>
@@ -24372,7 +24372,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="inlineStr"/>
@@ -24465,7 +24465,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="inlineStr"/>
@@ -24558,7 +24558,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="inlineStr"/>
@@ -24651,7 +24651,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="inlineStr"/>
@@ -24744,7 +24744,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="inlineStr"/>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="inlineStr"/>
@@ -24930,7 +24930,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="inlineStr"/>
@@ -25023,7 +25023,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="inlineStr"/>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="inlineStr"/>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="inlineStr"/>
@@ -25302,7 +25302,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="inlineStr"/>
@@ -25395,7 +25395,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="inlineStr"/>
@@ -25488,7 +25488,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="inlineStr"/>
@@ -25581,7 +25581,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="inlineStr"/>
@@ -25674,7 +25674,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="inlineStr"/>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="inlineStr"/>
@@ -25860,7 +25860,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="inlineStr"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="inlineStr"/>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="inlineStr"/>
@@ -26139,7 +26139,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="inlineStr"/>
@@ -26232,7 +26232,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="inlineStr"/>
@@ -26325,7 +26325,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="inlineStr"/>
@@ -26418,7 +26418,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="inlineStr"/>
@@ -26511,7 +26511,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="inlineStr"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="inlineStr"/>
@@ -26697,7 +26697,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="inlineStr"/>
@@ -26790,7 +26790,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="inlineStr"/>
@@ -26883,7 +26883,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="inlineStr"/>
@@ -26976,7 +26976,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="inlineStr"/>
@@ -27069,7 +27069,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="inlineStr"/>
@@ -27162,7 +27162,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="inlineStr"/>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="inlineStr"/>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="inlineStr"/>
@@ -27441,7 +27441,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="inlineStr"/>
@@ -27534,7 +27534,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="inlineStr"/>
@@ -27627,7 +27627,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="inlineStr"/>
@@ -27720,7 +27720,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="inlineStr"/>
@@ -27813,7 +27813,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="inlineStr"/>
@@ -27906,7 +27906,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="inlineStr"/>
@@ -27999,7 +27999,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="inlineStr"/>
@@ -28092,7 +28092,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="inlineStr"/>
@@ -28185,7 +28185,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="inlineStr"/>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="inlineStr"/>
@@ -28371,7 +28371,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="inlineStr"/>
@@ -28464,7 +28464,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="inlineStr"/>
@@ -28557,7 +28557,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="inlineStr"/>
@@ -28650,7 +28650,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="inlineStr"/>
@@ -28743,7 +28743,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="inlineStr"/>
@@ -28836,7 +28836,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="n">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="n">
@@ -29038,7 +29038,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="inlineStr"/>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>21-04-2021 08:30</t>
+          <t>2021-04-21 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="n">
@@ -29230,7 +29230,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="n">
@@ -29329,7 +29329,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>21-04-2021 08:30</t>
+          <t>2021-04-21 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="n">
@@ -29428,7 +29428,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="n">
@@ -29630,7 +29630,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="n">
@@ -29731,7 +29731,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="inlineStr"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="inlineStr"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="inlineStr"/>
@@ -30010,7 +30010,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="inlineStr"/>
@@ -30103,7 +30103,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="inlineStr"/>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="inlineStr"/>
@@ -30289,7 +30289,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="inlineStr"/>
@@ -30382,7 +30382,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="inlineStr"/>
@@ -30475,7 +30475,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="inlineStr"/>
@@ -30568,7 +30568,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="inlineStr"/>
@@ -30661,7 +30661,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="inlineStr"/>
@@ -30754,7 +30754,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="inlineStr"/>
@@ -30847,7 +30847,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="inlineStr"/>
@@ -30940,7 +30940,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="inlineStr"/>
@@ -31033,7 +31033,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="inlineStr"/>
@@ -31126,7 +31126,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="inlineStr"/>
@@ -31219,7 +31219,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="inlineStr"/>
@@ -31312,7 +31312,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="inlineStr"/>
@@ -31405,7 +31405,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="inlineStr"/>
@@ -31498,7 +31498,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="inlineStr"/>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="inlineStr"/>
@@ -31684,7 +31684,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="inlineStr"/>
@@ -31777,7 +31777,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="inlineStr"/>
@@ -31870,7 +31870,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="inlineStr"/>
@@ -31963,7 +31963,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="inlineStr"/>
@@ -32056,7 +32056,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="inlineStr"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="inlineStr"/>
@@ -32242,7 +32242,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="inlineStr"/>
@@ -32335,7 +32335,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="inlineStr"/>
@@ -32428,7 +32428,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="inlineStr"/>
@@ -32521,7 +32521,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="inlineStr"/>
@@ -32614,7 +32614,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="inlineStr"/>
@@ -32707,7 +32707,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="inlineStr"/>
@@ -32800,7 +32800,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="inlineStr"/>
@@ -32893,7 +32893,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="inlineStr"/>
@@ -32986,7 +32986,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="inlineStr"/>
@@ -33079,7 +33079,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="n">
@@ -33180,7 +33180,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="inlineStr"/>
@@ -33273,7 +33273,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="inlineStr"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="inlineStr"/>
@@ -33459,7 +33459,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -33552,7 +33552,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="n">
@@ -33651,7 +33651,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="n">
@@ -33750,7 +33750,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="inlineStr"/>
@@ -33843,7 +33843,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="inlineStr"/>
@@ -33936,7 +33936,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="inlineStr"/>
@@ -34029,7 +34029,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="inlineStr"/>
@@ -34122,7 +34122,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="inlineStr"/>
@@ -34215,7 +34215,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="inlineStr"/>
@@ -34308,7 +34308,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="inlineStr"/>
@@ -34401,7 +34401,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="inlineStr"/>
@@ -34494,7 +34494,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="inlineStr"/>
@@ -34587,7 +34587,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="n">
@@ -34682,7 +34682,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="n">
@@ -34777,7 +34777,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="n">
@@ -34872,7 +34872,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="n">
@@ -34967,7 +34967,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="n">
@@ -35062,7 +35062,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="n">
@@ -35157,7 +35157,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="n">
@@ -35252,7 +35252,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="n">
@@ -35347,7 +35347,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="n">
@@ -35442,7 +35442,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="n">
@@ -35537,7 +35537,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="inlineStr"/>
@@ -35630,7 +35630,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="n">
@@ -35725,7 +35725,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="n">
@@ -35820,7 +35820,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="n">
@@ -35915,7 +35915,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>17-08-2021 08:30</t>
+          <t>2021-08-17 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="n">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="n">
@@ -36105,7 +36105,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="n">
@@ -36200,7 +36200,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="n">
@@ -36295,7 +36295,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="n">
@@ -36390,7 +36390,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="n">
@@ -36489,7 +36489,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="n">
@@ -36588,7 +36588,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="n">
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="n">
@@ -36786,7 +36786,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>22-05-2021 08:30</t>
+          <t>2021-05-22 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="n">
@@ -36885,7 +36885,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>24-06-2021 08:30</t>
+          <t>2021-06-24 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="n">
@@ -36984,7 +36984,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="n">
@@ -37083,7 +37083,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="n">
@@ -37182,7 +37182,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="n">
@@ -37281,7 +37281,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="n">
@@ -37380,7 +37380,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="n">
@@ -37475,7 +37475,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="n">
@@ -37570,7 +37570,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="n">
@@ -37665,7 +37665,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="n">
@@ -37760,7 +37760,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>11-06-2021 08:30</t>
+          <t>2021-11-06 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="n">
@@ -37855,7 +37855,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="n">
@@ -37950,7 +37950,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>17-08-2021 08:30</t>
+          <t>2021-08-17 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="n">
@@ -38045,7 +38045,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="n">
@@ -38140,7 +38140,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="n">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>19-11-2021 08:30</t>
+          <t>2021-11-19 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="n">
@@ -38330,7 +38330,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="n">
